--- a/examples/answer_key.xlsx
+++ b/examples/answer_key.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,10 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,62 +484,82 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Поглощение: k хвоста при 400 нм, ×10⁻³</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Фактический угол, град</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Полоса, нм</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Сдвиг шкалы λ, нм</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>E0, эВ</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>C, эВ</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Eg, эВ</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>A_uv</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>A_k хвоста, эВ</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>n(450)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>n(550)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>n(650)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>n(750)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>k(450)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>k(550)</t>
         </is>
       </c>
     </row>
@@ -560,40 +584,52 @@
         <v>2.2</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>65.02</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>0.06</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>261.97</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>4.04</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>3.37</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>131.46</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>2.4249</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>2.3248</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>2.2784</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>2.2522</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -617,40 +653,52 @@
         <v>1.6</v>
       </c>
       <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>59.98</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>311.7</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="K3" s="2" t="n">
         <v>5.25</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>2.7</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>4.15</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>11.33</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>2.1832</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2.1285</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>2.1004</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>2.0838</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -674,40 +722,52 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>60.03</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>1.4</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>317.99</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>4.72</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>3.78</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>66.31</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
         <v>2.4002</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>2.3235</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>2.2854</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>2.2632</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -731,40 +791,52 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>70.01000000000001</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>161.21</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>101.24</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <v>2.0077</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>1.9807</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>1.9662</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>1.9574</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -788,51 +860,270 @@
         <v>0.9</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>391.02</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>6.15</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>2.85</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>5.16</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>17.49</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>2.0024</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>1.9724</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>1.9563</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>1.9466</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>06_SiNx_on_fused_silica_65deg.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SiNₓ:H (обогащённый Si) на плавленом кварце, 65°</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>712.6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1.0222</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>2.2725</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>2.2081</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>2.1747</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>2.1566</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.01905</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.00177</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>07_WO3_on_BK7_60deg.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>WO₃ на BK7, 60° (350–800 нм)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>838.2</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>304.79</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>2.0713</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>2.0176</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1.9925</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>1.9784</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.00047</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>08_CeO2_on_Si_65deg.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CeO₂ на кремнии, 65°</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>887.5</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>65.03</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>406.29</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>2.4354</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>2.3186</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>2.2719</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.00062</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.00022</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Дисперсия каждой плёнки отличается от справочной (силы осцилляторов, E0, C, Eg), как у реального образца; угол отличается от номинального на 0.01–0.03°; дрейф и шум добавлены.</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Дисперсия каждой плёнки отличается от справочной (силы осцилляторов, E0, C, Eg), как у реального образца; угол отличается от номинального на 0.01–0.03°; дрейф и шум добавлены. Поглощение задаётся хвостом ниже края (второй осциллятор Тауца–Лоренца с теми же E0, C, порог E_t = 1.2 эВ, сила A_k); k(450), k(550) — полный k плёнки (край материала + хвост); у образцов 01–05 хвоста нет.</t>
         </is>
       </c>
     </row>

--- a/examples/answer_key.xlsx
+++ b/examples/answer_key.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,7 @@
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,75 +490,80 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Задняя сторона: истинная доля (задано ± неопр.)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Фактический угол, град</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Полоса, нм</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Сдвиг шкалы λ, нм</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>E0, эВ</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>C, эВ</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Eg, эВ</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>A_uv</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>A_k хвоста, эВ</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>n(450)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>n(550)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>n(650)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>n(750)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>k(450)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>k(550)</t>
         </is>
@@ -586,49 +592,54 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>65.02</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>0.06</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>261.97</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>4.04</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>3.37</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>131.46</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>2.4249</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>2.3248</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>2.2784</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>2.2522</v>
       </c>
-      <c r="T2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -655,49 +666,54 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>59.98</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="K3" s="2" t="n">
         <v>311.7</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>5.25</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>2.7</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>4.15</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>11.33</v>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>2.1832</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>2.1285</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>2.1004</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="T3" s="2" t="n">
         <v>2.0838</v>
       </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -724,49 +740,54 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>60.03</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>1.4</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>317.99</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>4.72</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>3.78</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>66.31</v>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
         <v>2.4002</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>2.3235</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>2.2854</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="T4" s="2" t="n">
         <v>2.2632</v>
       </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -793,49 +814,54 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>70.01000000000001</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="K5" s="2" t="n">
         <v>161.21</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>101.24</v>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
         <v>2.0077</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>1.9807</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>1.9662</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>1.9574</v>
       </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -862,49 +888,54 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>391.02</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>6.15</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>2.85</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>5.16</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>17.49</v>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>2.0024</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>1.9724</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>1.9563</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="T6" s="2" t="n">
         <v>1.9466</v>
       </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -931,49 +962,54 @@
       <c r="F7" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>65.02</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>53.6</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>7.42</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>2.14</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="O7" s="2" t="n">
         <v>76.97</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>1.0222</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>2.2725</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>2.2081</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>2.1747</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>2.1566</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>0.01905</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="V7" s="2" t="n">
         <v>0.00177</v>
       </c>
     </row>
@@ -1000,49 +1036,54 @@
       <c r="F8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>60.02</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>58.36</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>1.24</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>304.79</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>0.1575</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>2.0713</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>2.0176</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>1.9925</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="T8" s="2" t="n">
         <v>1.9784</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="U8" s="2" t="n">
         <v>0.00115</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="V8" s="2" t="n">
         <v>0.00047</v>
       </c>
     </row>
@@ -1069,61 +1110,140 @@
       <c r="F9" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>65.03</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>66.89</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>3.94</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>2.79</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>406.29</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.0667</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>2.4354</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>2.3186</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>2.2719</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>2.247</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>0.00062</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="V9" s="2" t="n">
         <v>0.00022</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>09_ZrO2_on_fused_silica_1mm_backside_65deg.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ZrO₂ на плавленом кварце 1 мм с задней стороной, 65°</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>780.4</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0.960 (0.95 ± 0.02)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>455.73</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>2.2129</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>2.1761</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>2.1564</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>2.1446</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Дисперсия каждой плёнки отличается от справочной (силы осцилляторов, E0, C, Eg), как у реального образца; угол отличается от номинального на 0.01–0.03°; дрейф и шум добавлены. Поглощение задаётся хвостом ниже края (второй осциллятор Тауца–Лоренца с теми же E0, C, порог E_t = 1.2 эВ, сила A_k); k(450), k(550) — полный k плёнки (край материала + хвост); у образцов 01–05 хвоста нет.</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Дисперсия каждой плёнки отличается от справочной (силы осцилляторов, E0, C, Eg), как у реального образца; угол отличается от номинального на 0.01–0.03°; дрейф и шум добавлены. Поглощение задаётся хвостом ниже края (второй осциллятор Тауца–Лоренца с теми же E0, C, порог E_t = 1.2 эВ, сила A_k); k(450), k(550) — полный k плёнки (край материала + хвост); у образцов 01–05 хвоста нет. Задняя сторона подложки (образец 09): пучки, отражённые задней гранью плоскопараллельной подложки, складываются с передним некогерентно; доля собранного света задана из независимого измерения и не фитируется.</t>
         </is>
       </c>
     </row>
